--- a/CPRD Raw Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15.23</v>
+        <v>16.86</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>299</v>
       </c>
       <c r="E2">
-        <v>14.31</v>
+        <v>14.74</v>
       </c>
       <c r="F2">
-        <v>11.09</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2">
-        <v>14254</v>
+        <v>18046</v>
       </c>
       <c r="J2">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>16.65</v>
       </c>
       <c r="L2">
-        <v>15.47</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.619999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,28 +469,28 @@
         <v>159.58</v>
       </c>
       <c r="E3">
-        <v>12.36</v>
+        <v>12.84</v>
       </c>
       <c r="F3">
-        <v>4.01</v>
+        <v>5.01</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>13.02</v>
+        <v>14.02</v>
       </c>
       <c r="I3">
-        <v>14254</v>
+        <v>18046</v>
       </c>
       <c r="J3">
         <v>0.1</v>
       </c>
       <c r="K3">
-        <v>8.42</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L3">
-        <v>8.82</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>12.16</v>
+        <v>13.31</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -579,28 +579,28 @@
         <v>299</v>
       </c>
       <c r="E2">
-        <v>14.17</v>
+        <v>14.79</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>17856</v>
+        <v>22866</v>
       </c>
       <c r="J2">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>11.95</v>
+        <v>13.12</v>
       </c>
       <c r="L2">
-        <v>12.37</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="3">
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6.88</v>
+        <v>7.35</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -617,7 +617,7 @@
         <v>159.58</v>
       </c>
       <c r="E3">
-        <v>11.58</v>
+        <v>12.02</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -626,19 +626,19 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>10.01</v>
+        <v>11.02</v>
       </c>
       <c r="I3">
-        <v>17856</v>
+        <v>22866</v>
       </c>
       <c r="J3">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="K3">
-        <v>6.71</v>
+        <v>7.19</v>
       </c>
       <c r="L3">
-        <v>7.05</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_visits_OMOP-Adjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.86</v>
+        <v>17.1</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,7 +431,7 @@
         <v>299</v>
       </c>
       <c r="E2">
-        <v>14.74</v>
+        <v>14.69</v>
       </c>
       <c r="F2">
         <v>13</v>
@@ -443,16 +443,16 @@
         <v>22</v>
       </c>
       <c r="I2">
-        <v>18046</v>
+        <v>23073</v>
       </c>
       <c r="J2">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>16.65</v>
+        <v>16.91</v>
       </c>
       <c r="L2">
-        <v>17.08</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>9.31</v>
+        <v>12.05</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>159.58</v>
+        <v>191</v>
       </c>
       <c r="E3">
-        <v>12.84</v>
+        <v>13.26</v>
       </c>
       <c r="F3">
-        <v>5.01</v>
+        <v>9.01</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>14.02</v>
+        <v>17.02</v>
       </c>
       <c r="I3">
-        <v>18046</v>
+        <v>23073</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K3">
-        <v>9.119999999999999</v>
+        <v>11.88</v>
       </c>
       <c r="L3">
-        <v>9.5</v>
+        <v>12.22</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13.31</v>
+        <v>15.99</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -579,28 +579,28 @@
         <v>299</v>
       </c>
       <c r="E2">
-        <v>14.79</v>
+        <v>14.81</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>21.49</v>
       </c>
       <c r="I2">
-        <v>22866</v>
+        <v>24669</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="K2">
-        <v>13.12</v>
+        <v>15.81</v>
       </c>
       <c r="L2">
-        <v>13.5</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.35</v>
+        <v>11.27</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>159.58</v>
+        <v>191</v>
       </c>
       <c r="E3">
-        <v>12.02</v>
+        <v>13.16</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>8.01</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="H3">
-        <v>11.02</v>
+        <v>16.02</v>
       </c>
       <c r="I3">
-        <v>22866</v>
+        <v>24669</v>
       </c>
       <c r="J3">
         <v>0.08</v>
       </c>
       <c r="K3">
-        <v>7.19</v>
+        <v>11.1</v>
       </c>
       <c r="L3">
-        <v>7.5</v>
+        <v>11.43</v>
       </c>
     </row>
   </sheetData>
